--- a/Data/EXCEL/Transfer/salemon/202208/9912-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/9912-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88E6D2BA-9CEF-4D45-88E9-5FCF9CA62AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{85AEDA8E-E6D0-4759-A034-C6C79749A44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="9912-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,19 +1227,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q306"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="10.125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="11.625" customWidth="1"/>
-    <col min="8" max="13" width="10.125" customWidth="1"/>
-    <col min="14" max="14" width="9.5" customWidth="1"/>
-    <col min="15" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="13" width="14.125" customWidth="1"/>
+    <col min="14" max="14" width="13.375" customWidth="1"/>
+    <col min="15" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1258,7 +1265,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1297,7 +1304,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1340,7 +1347,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1379,7 +1386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1432,7 +1439,7 @@
         <v>-1.41</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1485,7 +1492,7 @@
         <v>-0.28000000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1538,7 +1545,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1591,7 +1598,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1644,7 +1651,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1697,7 +1704,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1750,7 +1757,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1803,7 +1810,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1856,7 +1863,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1909,7 +1916,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1962,7 +1969,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2015,7 +2022,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2068,7 +2075,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2121,7 +2128,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2174,7 +2181,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2227,7 +2234,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2280,7 +2287,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2333,7 +2340,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2386,7 +2393,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2439,7 +2446,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2492,7 +2499,7 @@
         <v>-9.8000000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2545,7 +2552,7 @@
         <v>-11.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2598,7 +2605,7 @@
         <v>-13.2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2651,7 +2658,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2704,7 +2711,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2757,7 +2764,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2810,7 +2817,7 @@
         <v>-22.2</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2863,7 +2870,7 @@
         <v>-19.7</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2916,7 +2923,7 @@
         <v>-20.8</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2969,7 +2976,7 @@
         <v>-12.9</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>-14.8</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3075,7 +3082,7 @@
         <v>-19.8</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3181,7 +3188,7 @@
         <v>-19.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3234,7 +3241,7 @@
         <v>-19.600000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3287,7 +3294,7 @@
         <v>-20.2</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3340,7 +3347,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3393,7 +3400,7 @@
         <v>-18.600000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3446,7 +3453,7 @@
         <v>-19.5</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3499,7 +3506,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3552,7 +3559,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3605,7 +3612,7 @@
         <v>-22.7</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3658,7 +3665,7 @@
         <v>-24.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3711,7 +3718,7 @@
         <v>-36.200000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3764,7 +3771,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3817,7 +3824,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3923,7 +3930,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3976,7 +3983,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4029,7 +4036,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4082,7 +4089,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4135,7 +4142,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4188,7 +4195,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4241,7 +4248,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4294,7 +4301,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4347,7 +4354,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4400,7 +4407,7 @@
         <v>-1.81</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4453,7 +4460,7 @@
         <v>-3.24</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4506,7 +4513,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4559,7 +4566,7 @@
         <v>-5.97</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4612,7 +4619,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4665,7 +4672,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4718,7 +4725,7 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4771,7 +4778,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4824,7 +4831,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4877,7 +4884,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4930,7 +4937,7 @@
         <v>-19.7</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4983,7 +4990,7 @@
         <v>-14.1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5036,7 +5043,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5089,7 +5096,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5142,7 +5149,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5195,7 +5202,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5248,7 +5255,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5301,7 +5308,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5354,7 +5361,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5407,7 +5414,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5460,7 +5467,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5513,7 +5520,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5566,7 +5573,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5619,7 +5626,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5672,7 +5679,7 @@
         <v>-0.32</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5725,7 +5732,7 @@
         <v>-0.88</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5778,7 +5785,7 @@
         <v>-0.55000000000000004</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5831,7 +5838,7 @@
         <v>-1.28</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5884,7 +5891,7 @@
         <v>-6.06</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5937,7 +5944,7 @@
         <v>-7.67</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5990,7 +5997,7 @@
         <v>-8.84</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6043,7 +6050,7 @@
         <v>-9.4700000000000006</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6096,7 +6103,7 @@
         <v>-6.58</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6149,7 +6156,7 @@
         <v>-4.8899999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6202,7 +6209,7 @@
         <v>-8.07</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6255,7 +6262,7 @@
         <v>-1.01</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6308,7 +6315,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6361,7 +6368,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6414,7 +6421,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6467,7 +6474,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6520,7 +6527,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6573,7 +6580,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6626,7 +6633,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6679,7 +6686,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6732,7 +6739,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6785,7 +6792,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6838,7 +6845,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6891,7 +6898,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6944,7 +6951,7 @@
         <v>-2.36</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6997,7 +7004,7 @@
         <v>-4.82</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7050,7 +7057,7 @@
         <v>-7.12</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7103,7 +7110,7 @@
         <v>-9.5399999999999991</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7156,7 +7163,7 @@
         <v>-9.5299999999999994</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7209,7 +7216,7 @@
         <v>-9.58</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7262,7 +7269,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7315,7 +7322,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7368,7 +7375,7 @@
         <v>-16.399999999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7421,7 +7428,7 @@
         <v>-15.6</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7474,7 +7481,7 @@
         <v>-11.9</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7527,7 +7534,7 @@
         <v>-15.7</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7580,7 +7587,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7633,7 +7640,7 @@
         <v>-9.06</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7686,7 +7693,7 @@
         <v>-8.56</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7739,7 +7746,7 @@
         <v>-8.17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7792,7 +7799,7 @@
         <v>-9.67</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7845,7 +7852,7 @@
         <v>-9.35</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7898,7 +7905,7 @@
         <v>-6.07</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7951,7 +7958,7 @@
         <v>-4.6500000000000004</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8004,7 +8011,7 @@
         <v>-4.04</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8057,7 +8064,7 @@
         <v>-5.94</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8110,7 +8117,7 @@
         <v>-5.18</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8163,7 +8170,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8216,7 +8223,7 @@
         <v>8.66</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8269,7 +8276,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8322,7 +8329,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8375,7 +8382,7 @@
         <v>8.02</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8428,7 +8435,7 @@
         <v>7.13</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8481,7 +8488,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8534,7 +8541,7 @@
         <v>9.89</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8587,7 +8594,7 @@
         <v>7.43</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8640,7 +8647,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8693,7 +8700,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8746,7 +8753,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8799,7 +8806,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8852,7 +8859,7 @@
         <v>-22.4</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8905,7 +8912,7 @@
         <v>-21.5</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8958,7 +8965,7 @@
         <v>-21.4</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9011,7 +9018,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9064,7 +9071,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9117,7 +9124,7 @@
         <v>-26</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9170,7 +9177,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9223,7 +9230,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9276,7 +9283,7 @@
         <v>-26.2</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9329,7 +9336,7 @@
         <v>-35.200000000000003</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9382,7 +9389,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9435,7 +9442,7 @@
         <v>-40.4</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9488,7 +9495,7 @@
         <v>-45.5</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9541,7 +9548,7 @@
         <v>-47.7</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9594,7 +9601,7 @@
         <v>-50</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9647,7 +9654,7 @@
         <v>-51.7</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9700,7 +9707,7 @@
         <v>-54</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9753,7 +9760,7 @@
         <v>-54.3</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9806,7 +9813,7 @@
         <v>-56.2</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9859,7 +9866,7 @@
         <v>-60.5</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9912,7 +9919,7 @@
         <v>-59.7</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9965,7 +9972,7 @@
         <v>-49.9</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10018,7 +10025,7 @@
         <v>-45.4</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10071,7 +10078,7 @@
         <v>-44.2</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10124,7 +10131,7 @@
         <v>-43.1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10177,7 +10184,7 @@
         <v>-42.8</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10230,7 +10237,7 @@
         <v>-40.200000000000003</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10283,7 +10290,7 @@
         <v>-39.9</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10336,7 +10343,7 @@
         <v>-35.200000000000003</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10389,7 +10396,7 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10442,7 +10449,7 @@
         <v>-23.5</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10495,7 +10502,7 @@
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10548,7 +10555,7 @@
         <v>-18.399999999999999</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10601,7 +10608,7 @@
         <v>-28.2</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10654,7 +10661,7 @@
         <v>-35.1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10707,7 +10714,7 @@
         <v>-29.6</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10760,7 +10767,7 @@
         <v>-24.2</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10813,7 +10820,7 @@
         <v>-23.1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10866,7 +10873,7 @@
         <v>-25.8</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10919,7 +10926,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10972,7 +10979,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11025,7 +11032,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11078,7 +11085,7 @@
         <v>-35.6</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11131,7 +11138,7 @@
         <v>-37.6</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11184,7 +11191,7 @@
         <v>-38.9</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11237,7 +11244,7 @@
         <v>-42.1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11290,7 +11297,7 @@
         <v>-39.299999999999997</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11343,7 +11350,7 @@
         <v>-45.2</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11396,7 +11403,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11449,7 +11456,7 @@
         <v>-19.5</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11502,7 +11509,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11555,7 +11562,7 @@
         <v>-8.65</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11608,7 +11615,7 @@
         <v>-4.6900000000000004</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11661,7 +11668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11714,7 +11721,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11767,7 +11774,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11820,7 +11827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11873,7 +11880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11926,7 +11933,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11979,7 +11986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12032,7 +12039,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12085,7 +12092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12138,7 +12145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12191,7 +12198,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12244,7 +12251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12297,7 +12304,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12350,7 +12357,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12403,7 +12410,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12456,7 +12463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12509,7 +12516,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12562,7 +12569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12615,7 +12622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12668,7 +12675,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12721,7 +12728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12774,7 +12781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12827,7 +12834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12880,7 +12887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12933,7 +12940,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12986,7 +12993,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13039,7 +13046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13092,7 +13099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13145,7 +13152,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13198,7 +13205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13251,7 +13258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13304,7 +13311,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13357,7 +13364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13410,7 +13417,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13463,7 +13470,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13516,7 +13523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13569,7 +13576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13622,7 +13629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13675,7 +13682,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13728,7 +13735,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13781,7 +13788,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13834,7 +13841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13887,7 +13894,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" s="5" customFormat="1">
+    <row r="241" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>37591</v>
       </c>
@@ -13940,7 +13947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" s="5" customFormat="1">
+    <row r="242" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>37561</v>
       </c>
@@ -13993,7 +14000,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" s="5" customFormat="1">
+    <row r="243" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>37530</v>
       </c>
@@ -14046,7 +14053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" s="5" customFormat="1">
+    <row r="244" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>37500</v>
       </c>
@@ -14099,7 +14106,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" s="5" customFormat="1">
+    <row r="245" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>37469</v>
       </c>
@@ -14152,7 +14159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" s="5" customFormat="1">
+    <row r="246" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>37438</v>
       </c>
@@ -14205,7 +14212,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" s="5" customFormat="1">
+    <row r="247" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>37408</v>
       </c>
@@ -14258,7 +14265,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" s="5" customFormat="1">
+    <row r="248" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>37377</v>
       </c>
@@ -14311,7 +14318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1">
+    <row r="249" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>37347</v>
       </c>
@@ -14364,7 +14371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1">
+    <row r="250" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>37316</v>
       </c>
@@ -14417,7 +14424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1">
+    <row r="251" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>37288</v>
       </c>
@@ -14470,7 +14477,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1">
+    <row r="252" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>37257</v>
       </c>
@@ -14523,7 +14530,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:17" s="5" customFormat="1">
+    <row r="253" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>37226</v>
       </c>
@@ -14576,7 +14583,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:17" s="5" customFormat="1">
+    <row r="254" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>37196</v>
       </c>
@@ -14629,7 +14636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:17" s="5" customFormat="1">
+    <row r="255" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>37165</v>
       </c>
@@ -14682,7 +14689,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:17" s="5" customFormat="1">
+    <row r="256" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>37135</v>
       </c>
@@ -14735,7 +14742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:17" s="5" customFormat="1">
+    <row r="257" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>37104</v>
       </c>
@@ -14788,7 +14795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:17" s="5" customFormat="1">
+    <row r="258" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>37073</v>
       </c>
@@ -14841,7 +14848,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:17" s="5" customFormat="1">
+    <row r="259" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>37043</v>
       </c>
@@ -14894,7 +14901,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="260" spans="1:17" s="5" customFormat="1">
+    <row r="260" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>37012</v>
       </c>
@@ -14947,7 +14954,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:17" s="5" customFormat="1">
+    <row r="261" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>36982</v>
       </c>
@@ -15000,7 +15007,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:17" s="5" customFormat="1">
+    <row r="262" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>36951</v>
       </c>
@@ -15053,7 +15060,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:17" s="5" customFormat="1">
+    <row r="263" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>36923</v>
       </c>
@@ -15106,7 +15113,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:17" s="5" customFormat="1">
+    <row r="264" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>36892</v>
       </c>
@@ -15159,7 +15166,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:17" s="5" customFormat="1">
+    <row r="265" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>36861</v>
       </c>
@@ -15212,7 +15219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:17" s="5" customFormat="1">
+    <row r="266" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>36831</v>
       </c>
@@ -15265,7 +15272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:17" s="5" customFormat="1">
+    <row r="267" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>36800</v>
       </c>
@@ -15318,7 +15325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:17" s="5" customFormat="1">
+    <row r="268" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>36770</v>
       </c>
@@ -15371,7 +15378,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:17" s="5" customFormat="1">
+    <row r="269" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>36739</v>
       </c>
@@ -15424,7 +15431,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:17" s="5" customFormat="1">
+    <row r="270" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>36708</v>
       </c>
@@ -15477,7 +15484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:17" s="5" customFormat="1">
+    <row r="271" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>36678</v>
       </c>
@@ -15530,7 +15537,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:17" s="5" customFormat="1">
+    <row r="272" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>36647</v>
       </c>
@@ -15583,7 +15590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:17" s="5" customFormat="1">
+    <row r="273" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>36617</v>
       </c>
@@ -15636,7 +15643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:17" s="5" customFormat="1">
+    <row r="274" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>36586</v>
       </c>
@@ -15689,7 +15696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:17" s="5" customFormat="1">
+    <row r="275" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>36557</v>
       </c>
@@ -15742,7 +15749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:17" s="5" customFormat="1">
+    <row r="276" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>36526</v>
       </c>
@@ -15795,7 +15802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:17" s="5" customFormat="1">
+    <row r="277" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>36495</v>
       </c>
@@ -15848,7 +15855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="278" spans="1:17" s="5" customFormat="1">
+    <row r="278" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>36465</v>
       </c>
@@ -15901,7 +15908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:17" s="5" customFormat="1">
+    <row r="279" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>36434</v>
       </c>
@@ -15954,7 +15961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="280" spans="1:17" s="5" customFormat="1">
+    <row r="280" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>36404</v>
       </c>
@@ -16007,7 +16014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:17" s="5" customFormat="1">
+    <row r="281" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>36373</v>
       </c>
@@ -16060,7 +16067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:17" s="5" customFormat="1">
+    <row r="282" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>36342</v>
       </c>
@@ -16113,7 +16120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:17" s="5" customFormat="1">
+    <row r="283" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>36312</v>
       </c>
@@ -16166,7 +16173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:17" s="5" customFormat="1">
+    <row r="284" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>36281</v>
       </c>
@@ -16219,7 +16226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:17" s="5" customFormat="1">
+    <row r="285" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>36251</v>
       </c>
@@ -16272,7 +16279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:17" s="5" customFormat="1">
+    <row r="286" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>36220</v>
       </c>
@@ -16325,7 +16332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:17" s="5" customFormat="1">
+    <row r="287" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>36192</v>
       </c>
@@ -16378,7 +16385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:17" s="5" customFormat="1">
+    <row r="288" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>36161</v>
       </c>
@@ -16431,7 +16438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:17" s="5" customFormat="1">
+    <row r="289" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>36130</v>
       </c>
@@ -16484,7 +16491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" spans="1:17" s="5" customFormat="1">
+    <row r="290" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>36100</v>
       </c>
@@ -16537,7 +16544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="291" spans="1:17" s="5" customFormat="1">
+    <row r="291" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>36069</v>
       </c>
@@ -16590,7 +16597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" spans="1:17" s="5" customFormat="1">
+    <row r="292" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>36039</v>
       </c>
@@ -16643,7 +16650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="293" spans="1:17" s="5" customFormat="1">
+    <row r="293" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>36008</v>
       </c>
@@ -16696,7 +16703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:17" s="5" customFormat="1">
+    <row r="294" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>35977</v>
       </c>
@@ -16749,7 +16756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:17" s="5" customFormat="1">
+    <row r="295" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>35947</v>
       </c>
@@ -16802,7 +16809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:17" s="5" customFormat="1">
+    <row r="296" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>35916</v>
       </c>
@@ -16855,7 +16862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:17" s="5" customFormat="1">
+    <row r="297" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>35886</v>
       </c>
@@ -16908,7 +16915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:17" s="5" customFormat="1">
+    <row r="298" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>35827</v>
       </c>
@@ -16961,7 +16968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="1:17" s="5" customFormat="1">
+    <row r="299" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>35796</v>
       </c>
@@ -17014,7 +17021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="300" spans="1:17" s="5" customFormat="1">
+    <row r="300" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A300" s="6">
         <v>35765</v>
       </c>
@@ -17067,7 +17074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="301" spans="1:17" s="5" customFormat="1">
+    <row r="301" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>35735</v>
       </c>
@@ -17120,7 +17127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="302" spans="1:17" s="5" customFormat="1">
+    <row r="302" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>35704</v>
       </c>
@@ -17173,7 +17180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="303" spans="1:17" s="5" customFormat="1">
+    <row r="303" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>35674</v>
       </c>
@@ -17226,7 +17233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="304" spans="1:17" s="5" customFormat="1">
+    <row r="304" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>35643</v>
       </c>
@@ -17279,7 +17286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="305" spans="1:17" s="5" customFormat="1">
+    <row r="305" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A305" s="6">
         <v>35612</v>
       </c>
@@ -17332,7 +17339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="306" spans="1:17" s="5" customFormat="1">
+    <row r="306" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A306" s="6">
         <v>35582</v>
       </c>
@@ -17400,7 +17407,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>